--- a/data/trans_orig/IQ3002_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3002_MoAR-Clase-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses en la que empezaron a comer cereales con gluten</t>
+          <t>Meses en la que empezaron a comer cereales con gluten (tasa de respuesta: 55,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 10,24</t>
+          <t>7,16; 10,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,18; 9,4</t>
+          <t>7,16; 9,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,73</t>
+          <t>5,85; 7,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 7,43</t>
+          <t>6,25; 7,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 7,7</t>
+          <t>6,09; 7,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 8,23</t>
+          <t>5,89; 8,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,89; 8,55</t>
+          <t>6,94; 8,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 8,33</t>
+          <t>6,88; 8,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 7,68</t>
+          <t>6,16; 7,64</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 7,03</t>
+          <t>5,77; 7,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 9,89</t>
+          <t>6,71; 9,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 9,23</t>
+          <t>5,53; 9,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,84</t>
+          <t>6,23; 8,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 8,88</t>
+          <t>6,08; 9,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,57</t>
+          <t>6,15; 8,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 8,23</t>
+          <t>6,29; 8,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 8,83</t>
+          <t>6,7; 8,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 8,17</t>
+          <t>6,02; 8,3</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,54</t>
+          <t>5,95; 8,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 11,09</t>
+          <t>8,12; 10,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 9,56</t>
+          <t>5,74; 9,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,19</t>
+          <t>6,83; 10,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 9,22</t>
+          <t>6,71; 9,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,1</t>
+          <t>5,94; 10,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,68; 8,89</t>
+          <t>6,68; 9,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,47; 9,42</t>
+          <t>7,49; 9,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 9,09</t>
+          <t>6,4; 9,15</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 8,45</t>
+          <t>6,4; 8,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 9,1</t>
+          <t>7,05; 9,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,54; 8,58</t>
+          <t>6,51; 8,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,52; 6,39</t>
+          <t>5,52; 6,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 8,89</t>
+          <t>7,06; 8,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 7,25</t>
+          <t>5,86; 7,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 7,29</t>
+          <t>6,09; 7,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 8,56</t>
+          <t>7,31; 8,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 7,75</t>
+          <t>6,48; 7,77</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,92</t>
+          <t>4,84; 6,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 8,63</t>
+          <t>6,53; 8,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 10,49</t>
+          <t>7,4; 10,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,67; 6,55</t>
+          <t>4,76; 6,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,7; 9,93</t>
+          <t>7,67; 10,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,42; 8,92</t>
+          <t>6,42; 8,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 6,62</t>
+          <t>5,27; 6,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 9,01</t>
+          <t>7,41; 9,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,28; 9,16</t>
+          <t>7,3; 9,31</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,07; 7,92</t>
+          <t>6,1; 8,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,76; 6,94</t>
+          <t>4,69; 6,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,18; 7,64</t>
+          <t>5,18; 7,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,82; 7,79</t>
+          <t>5,79; 7,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,58; 8,26</t>
+          <t>5,53; 8,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,87; 9,0</t>
+          <t>6,87; 9,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,59</t>
+          <t>6,18; 7,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 7,35</t>
+          <t>5,46; 7,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,11; 7,75</t>
+          <t>6,02; 7,7</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,64; 7,74</t>
+          <t>6,65; 7,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,44; 8,47</t>
+          <t>7,44; 8,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,64; 7,8</t>
+          <t>6,62; 7,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,43; 7,27</t>
+          <t>6,41; 7,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,29; 8,27</t>
+          <t>7,25; 8,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,59; 7,55</t>
+          <t>6,59; 7,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,65; 7,3</t>
+          <t>6,65; 7,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,19</t>
+          <t>7,45; 8,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,77; 7,53</t>
+          <t>6,75; 7,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3002_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3002_MoAR-Clase-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 10,61</t>
+          <t>7,22; 10,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 9,4</t>
+          <t>7,12; 9,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 7,64</t>
+          <t>5,89; 7,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 7,4</t>
+          <t>6,2; 7,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 7,65</t>
+          <t>6,12; 7,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 8,13</t>
+          <t>5,94; 8,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 8,53</t>
+          <t>6,87; 8,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 8,36</t>
+          <t>6,88; 8,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 7,64</t>
+          <t>6,17; 7,71</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 7,02</t>
+          <t>5,8; 7,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 9,74</t>
+          <t>6,74; 10,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,17</t>
+          <t>5,43; 9,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 8,93</t>
+          <t>6,23; 8,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 9,18</t>
+          <t>6,04; 9,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 8,55</t>
+          <t>6,27; 8,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,29; 8,28</t>
+          <t>6,28; 8,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 8,72</t>
+          <t>6,65; 8,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,3</t>
+          <t>6,11; 8,3</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,95; 8,1</t>
+          <t>5,99; 8,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 10,92</t>
+          <t>8,04; 11,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,67</t>
+          <t>5,77; 9,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 10,24</t>
+          <t>6,78; 10,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,71; 9,31</t>
+          <t>6,68; 9,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 10,2</t>
+          <t>5,77; 10,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,68; 9,01</t>
+          <t>6,63; 8,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 9,52</t>
+          <t>7,56; 9,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,15</t>
+          <t>6,33; 9,46</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 8,64</t>
+          <t>6,35; 8,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 9,1</t>
+          <t>7,02; 9,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 8,67</t>
+          <t>6,45; 8,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,52; 6,37</t>
+          <t>5,49; 6,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 8,82</t>
+          <t>7,17; 8,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 7,26</t>
+          <t>5,86; 7,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 7,43</t>
+          <t>6,04; 7,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,31; 8,6</t>
+          <t>7,33; 8,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 7,77</t>
+          <t>6,44; 7,77</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 8,78</t>
+          <t>6,54; 8,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1132,32 +1132,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 6,61</t>
+          <t>4,64; 6,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,67; 10,11</t>
+          <t>7,67; 9,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,42; 8,78</t>
+          <t>6,48; 8,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 6,59</t>
+          <t>5,21; 6,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 9,0</t>
+          <t>7,37; 9,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,3; 9,31</t>
+          <t>7,2; 9,15</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,04</t>
+          <t>6,07; 7,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,69; 6,92</t>
+          <t>4,68; 6,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,18; 7,77</t>
+          <t>5,22; 7,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,79; 7,82</t>
+          <t>5,9; 7,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,21</t>
+          <t>5,4; 8,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,87; 9,09</t>
+          <t>6,79; 9,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,18; 7,61</t>
+          <t>6,29; 7,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,46; 7,29</t>
+          <t>5,5; 7,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,7</t>
+          <t>6,07; 7,83</t>
         </is>
       </c>
     </row>
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,65; 7,78</t>
+          <t>6,66; 7,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,44; 8,46</t>
+          <t>7,45; 8,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,8</t>
+          <t>6,65; 7,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,41; 7,23</t>
+          <t>6,45; 7,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1362,22 +1362,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,59; 7,53</t>
+          <t>6,62; 7,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,65; 7,29</t>
+          <t>6,63; 7,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 8,18</t>
+          <t>7,49; 8,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,75; 7,48</t>
+          <t>6,76; 7,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3002_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3002_MoAR-Clase-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,81</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,96</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,84</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>8,33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,34</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,72</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,81</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,96</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,84</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,22; 10,42</t>
+          <t>6,24; 7,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,12; 9,36</t>
+          <t>6,06; 7,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 7,81</t>
+          <t>5,94; 8,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 7,46</t>
+          <t>7,16; 10,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 7,7</t>
+          <t>7,18; 9,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 8,1</t>
+          <t>5,83; 7,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 8,58</t>
+          <t>6,89; 8,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,88; 8,33</t>
+          <t>6,91; 8,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 7,71</t>
+          <t>6,18; 7,68</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,66</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,32</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,19</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,36</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>7,64</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>6,71</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,66</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,32</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 7,14</t>
+          <t>6,18; 8,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 10,14</t>
+          <t>6,08; 8,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 9,27</t>
+          <t>6,18; 8,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 8,96</t>
+          <t>5,77; 7,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,04; 9,06</t>
+          <t>6,7; 9,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,66</t>
+          <t>5,43; 9,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,19</t>
+          <t>6,24; 8,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,65; 8,79</t>
+          <t>6,7; 8,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 8,3</t>
+          <t>6,06; 8,17</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,02</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,78</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,55</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,67</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>9,31</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7,7</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,02</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,78</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,24</t>
+          <t>6,76; 10,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 11,19</t>
+          <t>6,73; 9,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 9,59</t>
+          <t>5,85; 10,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,78; 10,01</t>
+          <t>5,99; 8,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,68; 9,13</t>
+          <t>8,15; 11,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 10,11</t>
+          <t>5,72; 9,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 8,75</t>
+          <t>6,68; 8,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 9,55</t>
+          <t>7,47; 9,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,46</t>
+          <t>6,27; 9,09</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,98</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,96</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,54</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>7,16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>7,9</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,49</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,98</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,96</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,54</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 8,63</t>
+          <t>5,52; 6,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 9,08</t>
+          <t>7,12; 8,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 8,55</t>
+          <t>5,92; 7,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 6,39</t>
+          <t>6,3; 8,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 8,83</t>
+          <t>7,06; 9,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 7,29</t>
+          <t>6,54; 8,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 7,37</t>
+          <t>6,09; 7,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 8,7</t>
+          <t>7,3; 8,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 7,77</t>
+          <t>6,37; 7,75</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,87</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8,69</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,55</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>7,64</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>9,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,87</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,69</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,55</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 6,98</t>
+          <t>4,67; 6,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,54; 8,75</t>
+          <t>7,7; 9,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 10,46</t>
+          <t>6,42; 8,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 6,55</t>
+          <t>4,6; 6,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,67; 9,98</t>
+          <t>6,49; 8,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,86</t>
+          <t>7,52; 10,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,21; 6,62</t>
+          <t>5,2; 6,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,04</t>
+          <t>7,42; 9,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 9,15</t>
+          <t>7,28; 9,16</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7,01</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6,92</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7,53</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>6,95</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>5,93</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6,18</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7,01</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6,92</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,53</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,07; 7,99</t>
+          <t>5,82; 7,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,68; 6,94</t>
+          <t>5,58; 8,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,22; 7,88</t>
+          <t>6,87; 9,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,9; 7,79</t>
+          <t>6,07; 7,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,21</t>
+          <t>4,76; 6,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,79; 9,01</t>
+          <t>5,18; 7,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,29; 7,66</t>
+          <t>6,26; 7,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,5; 7,34</t>
+          <t>5,48; 7,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,07; 7,83</t>
+          <t>6,11; 7,75</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7,74</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7,06</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>7,12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>7,93</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>7,19</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6,8</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,74</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,06</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,66; 7,78</t>
+          <t>6,43; 7,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 8,51</t>
+          <t>7,29; 8,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,65; 7,89</t>
+          <t>6,59; 7,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,45; 7,25</t>
+          <t>6,64; 7,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 8,21</t>
+          <t>7,44; 8,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,55</t>
+          <t>6,64; 7,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,63; 7,32</t>
+          <t>6,65; 7,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,49; 8,19</t>
+          <t>7,46; 8,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,76; 7,5</t>
+          <t>6,77; 7,53</t>
         </is>
       </c>
     </row>
